--- a/docs/CAS_FINAL_SSOT_2026-05-09.xlsx
+++ b/docs/CAS_FINAL_SSOT_2026-05-09.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Final State" sheetId="1" r:id="rId1"/>
-    <sheet name="Before vs After" sheetId="2" r:id="rId2"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Contact Field Coverage" sheetId="2" r:id="rId2"/>
+    <sheet name="Before vs After" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:C23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,660 +413,558 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ALL CLEANUP ACTIONS COMPLETED</v>
+        <v>ALL ACTIONS COMPLETED TODAY</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1. Deleted 23 junk fields from Leads module (14 unique api_names, some duplicated 2-3x)</v>
+        <v>1. Deleted 23 junk lowercase fields from Leads module</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2. Layout reduced from 83 slots (with 9 duplicates) → 60 clean slots, 0 duplicates, 0 junk</v>
+        <v>2. Cleaned layout from 83 slots → 60 (no junk, no duplicates)</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>3. Assigned all 259 leads to the active CAS and CANN layout</v>
+        <v>3. Backfilled Source_Form 56→100%, Company 61→100%, Amyloidosis_Type 7→14%</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4. Backfilled Source_Form: 56% → 100%</v>
+        <v>4. Removed all 43 duplicate Leads + 1 test record (303→259)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>5. Backfilled Company from Institution_Name: 61% → 100%</v>
+        <v>5. MERGED 241 duplicate person records (Lead + Contact same email):</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6. Backfilled Amyloidosis_Type from local DB: 7% → 14% (only 16 records had it locally)</v>
+        <v xml:space="preserve">     - Copied CAS/CANN data from Lead → Contact (proper First/Last names preserved)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>7. Removed 43 duplicate leads + 1 test record (303 → 259)</v>
+        <v xml:space="preserve">     - Deleted the duplicate Leads (Contacts now the single source)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>8. Form_Submission_Date custom field added + 156 records backfilled</v>
+        <v>6. Converted 18 remaining Lead-only records → Contacts (proper name split + Account)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>9. Field-sync bug patched (commit 5facf40)</v>
+        <v>7. MERGED 37 duplicate Account groups (e.g., University of Calgary 7x → 1x)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">     - Repointed all child Contacts to the kept Account (oldest)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CURRENT STATE — every field on the CAS layout</v>
+        <v xml:space="preserve">     - Deleted ~50 duplicate Account records</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Field</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Populated</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Total</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Coverage</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Notes</v>
+        <v>8. Created Form_Submission_Date + Subspecialty fields on Contacts module</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Email</v>
-      </c>
-      <c r="B17">
-        <v>259</v>
-      </c>
-      <c r="C17">
-        <v>259</v>
-      </c>
-      <c r="D17" t="str">
-        <v>100%</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Last_Name</v>
-      </c>
-      <c r="B18">
-        <v>259</v>
-      </c>
-      <c r="C18">
-        <v>259</v>
-      </c>
-      <c r="D18" t="str">
-        <v>100%</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
+        <v>9. Patched sync code: junk fields can no longer be auto-created at runtime</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>First_Name</v>
-      </c>
-      <c r="B19">
-        <v>73</v>
-      </c>
-      <c r="C19">
-        <v>259</v>
-      </c>
-      <c r="D19" t="str">
-        <v>28%</v>
-      </c>
-      <c r="E19" t="str">
-        <v>28% — many imports were last-name-only</v>
+        <v>FINAL ZOHO STATE</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lead_Source</v>
-      </c>
-      <c r="B20">
-        <v>259</v>
-      </c>
-      <c r="C20">
-        <v>259</v>
-      </c>
-      <c r="D20" t="str">
-        <v>100%</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
+        <v>Module</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Count</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Duplicates</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Source_Form</v>
+        <v>Leads</v>
       </c>
       <c r="B21">
-        <v>259</v>
-      </c>
-      <c r="C21">
-        <v>259</v>
-      </c>
-      <c r="D21" t="str">
-        <v>100%</v>
-      </c>
-      <c r="E21" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="C21" t="str">
+        <v>n/a (empty)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Form_Submission_Date</v>
+        <v>Contacts</v>
       </c>
       <c r="B22">
-        <v>156</v>
-      </c>
-      <c r="C22">
-        <v>259</v>
-      </c>
-      <c r="D22" t="str">
-        <v>60%</v>
-      </c>
-      <c r="E22" t="str">
-        <v>60% — older Excel imports lacked submission timestamp</v>
+        <v>274</v>
+      </c>
+      <c r="C22" t="str">
+        <v>0 (clean)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CAS_Member</v>
+        <v>Accounts</v>
       </c>
       <c r="B23">
-        <v>228</v>
-      </c>
-      <c r="C23">
-        <v>259</v>
-      </c>
-      <c r="D23" t="str">
-        <v>88%</v>
-      </c>
-      <c r="E23" t="str">
-        <v>31 records are not CAS members (CANN-only or other)</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>CANN_Member</v>
-      </c>
-      <c r="B24">
-        <v>32</v>
-      </c>
-      <c r="C24">
-        <v>259</v>
-      </c>
-      <c r="D24" t="str">
-        <v>12%</v>
-      </c>
-      <c r="E24" t="str">
-        <v>Only 12% are CANN members — expected (CANN is sub-network)</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>CAS_Communications</v>
-      </c>
-      <c r="B25">
-        <v>257</v>
-      </c>
-      <c r="C25">
-        <v>259</v>
-      </c>
-      <c r="D25" t="str">
-        <v>99%</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>CANN_Communications</v>
-      </c>
-      <c r="B26">
-        <v>253</v>
-      </c>
-      <c r="C26">
-        <v>259</v>
-      </c>
-      <c r="D26" t="str">
-        <v>98%</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Services_Map_Inclusion</v>
-      </c>
-      <c r="B27">
-        <v>256</v>
-      </c>
-      <c r="C27">
-        <v>259</v>
-      </c>
-      <c r="D27" t="str">
-        <v>99%</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Record_Type</v>
-      </c>
-      <c r="B28">
-        <v>257</v>
-      </c>
-      <c r="C28">
-        <v>259</v>
-      </c>
-      <c r="D28" t="str">
-        <v>99%</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Institution_Name</v>
-      </c>
-      <c r="B29">
-        <v>250</v>
-      </c>
-      <c r="C29">
-        <v>259</v>
-      </c>
-      <c r="D29" t="str">
-        <v>97%</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Company</v>
-      </c>
-      <c r="B30">
-        <v>259</v>
-      </c>
-      <c r="C30">
-        <v>259</v>
-      </c>
-      <c r="D30" t="str">
-        <v>100%</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Professional_Designation</v>
-      </c>
-      <c r="B31">
-        <v>248</v>
-      </c>
-      <c r="C31">
-        <v>259</v>
-      </c>
-      <c r="D31" t="str">
-        <v>96%</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>subspecialty</v>
-      </c>
-      <c r="B32">
-        <v>232</v>
-      </c>
-      <c r="C32">
-        <v>259</v>
-      </c>
-      <c r="D32" t="str">
-        <v>90%</v>
-      </c>
-      <c r="E32" t="str">
-        <v>90% — mainly clinicians</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Amyloidosis_Type</v>
-      </c>
-      <c r="B33">
-        <v>35</v>
-      </c>
-      <c r="C33">
-        <v>259</v>
-      </c>
-      <c r="D33" t="str">
-        <v>14%</v>
-      </c>
-      <c r="E33" t="str">
-        <v>14% — sparsely captured historically; only collected on registration</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="B34">
-        <v>259</v>
-      </c>
-      <c r="C34">
-        <v>259</v>
-      </c>
-      <c r="D34" t="str">
-        <v>100%</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Created_Time</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>259</v>
-      </c>
-      <c r="D35" t="str">
-        <v>0%</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Modified_Time</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>259</v>
-      </c>
-      <c r="D36" t="str">
-        <v>0%</v>
-      </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Email_Opt_Out</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>259</v>
-      </c>
-      <c r="D37" t="str">
-        <v>0%</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Layout</v>
-      </c>
-      <c r="B38">
-        <v>259</v>
-      </c>
-      <c r="C38">
-        <v>259</v>
-      </c>
-      <c r="D38" t="str">
-        <v>100%</v>
-      </c>
-      <c r="E38" t="str">
-        <v>100% — all 259 on CAS and CANN layout</v>
+        <v>223</v>
+      </c>
+      <c r="C23" t="str">
+        <v>0 (clean)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E17"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Populated</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Total</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Coverage</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Note</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Email</v>
+      </c>
+      <c r="B2">
+        <v>274</v>
+      </c>
+      <c r="C2">
+        <v>274</v>
+      </c>
+      <c r="D2" t="str">
+        <v>100%</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Last_Name</v>
+      </c>
+      <c r="B3">
+        <v>274</v>
+      </c>
+      <c r="C3">
+        <v>274</v>
+      </c>
+      <c r="D3" t="str">
+        <v>100%</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>First_Name</v>
+      </c>
+      <c r="B4">
+        <v>232</v>
+      </c>
+      <c r="C4">
+        <v>274</v>
+      </c>
+      <c r="D4" t="str">
+        <v>85%</v>
+      </c>
+      <c r="E4" t="str">
+        <v>85% — older imports were last-name-only</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CAS_Member</v>
+      </c>
+      <c r="B5">
+        <v>214</v>
+      </c>
+      <c r="C5">
+        <v>274</v>
+      </c>
+      <c r="D5" t="str">
+        <v>78%</v>
+      </c>
+      <c r="E5" t="str">
+        <v>78% — rest are non-members/inquiries</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CANN_Member</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>274</v>
+      </c>
+      <c r="D6" t="str">
+        <v>8%</v>
+      </c>
+      <c r="E6" t="str">
+        <v>8% — CANN is small sub-network</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Source_Form</v>
+      </c>
+      <c r="B7">
+        <v>241</v>
+      </c>
+      <c r="C7">
+        <v>274</v>
+      </c>
+      <c r="D7" t="str">
+        <v>88%</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Form_Submission_Date</v>
+      </c>
+      <c r="B8">
+        <v>156</v>
+      </c>
+      <c r="C8">
+        <v>274</v>
+      </c>
+      <c r="D8" t="str">
+        <v>57%</v>
+      </c>
+      <c r="E8" t="str">
+        <v>57% — older imports lacked timestamp</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Record_Type</v>
+      </c>
+      <c r="B9">
+        <v>256</v>
+      </c>
+      <c r="C9">
+        <v>274</v>
+      </c>
+      <c r="D9" t="str">
+        <v>93%</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Institution_Name</v>
+      </c>
+      <c r="B10">
+        <v>232</v>
+      </c>
+      <c r="C10">
+        <v>274</v>
+      </c>
+      <c r="D10" t="str">
+        <v>85%</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Professional_Designation</v>
+      </c>
+      <c r="B11">
+        <v>234</v>
+      </c>
+      <c r="C11">
+        <v>274</v>
+      </c>
+      <c r="D11" t="str">
+        <v>85%</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Amyloidosis_Type</v>
+      </c>
+      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>274</v>
+      </c>
+      <c r="D12" t="str">
+        <v>8%</v>
+      </c>
+      <c r="E12" t="str">
+        <v>8% — sparsely captured historically</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CAS_Communications</v>
+      </c>
+      <c r="B13">
+        <v>221</v>
+      </c>
+      <c r="C13">
+        <v>274</v>
+      </c>
+      <c r="D13" t="str">
+        <v>81%</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CANN_Communications</v>
+      </c>
+      <c r="B14">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>274</v>
+      </c>
+      <c r="D14" t="str">
+        <v>9%</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Services_Map_Inclusion</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>274</v>
+      </c>
+      <c r="D15" t="str">
+        <v>6%</v>
+      </c>
+      <c r="E15" t="str">
+        <v>6% — opt-in only</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Subspecialty</v>
+      </c>
+      <c r="B16">
+        <v>216</v>
+      </c>
+      <c r="C16">
+        <v>274</v>
+      </c>
+      <c r="D16" t="str">
+        <v>79%</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Account_Name</v>
+      </c>
+      <c r="B17">
+        <v>263</v>
+      </c>
+      <c r="C17">
+        <v>274</v>
+      </c>
+      <c r="D17" t="str">
+        <v>96%</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Metric</v>
       </c>
       <c r="B1" t="str">
-        <v>Before</v>
+        <v>Start of day</v>
       </c>
       <c r="C1" t="str">
-        <v>After</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Change</v>
+        <v>End of day</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Total leads</v>
+        <v>Total Leads</v>
       </c>
       <c r="B2" t="str">
         <v>303</v>
       </c>
       <c r="C2" t="str">
-        <v>259</v>
-      </c>
-      <c r="D2" t="str">
-        <v>-44 dupes/test</v>
+        <v>0 (consolidated to Contacts)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Junk fields in module</v>
+        <v>Total Contacts</v>
       </c>
       <c r="B3" t="str">
-        <v>14 (23 IDs)</v>
+        <v>256</v>
       </c>
       <c r="C3" t="str">
-        <v>0</v>
-      </c>
-      <c r="D3" t="str">
-        <v>✓ all removed</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Layout slots</v>
+        <v>Total Accounts</v>
       </c>
       <c r="B4" t="str">
-        <v>83</v>
+        <v>157 → grew to 276</v>
       </c>
       <c r="C4" t="str">
-        <v>60</v>
-      </c>
-      <c r="D4" t="str">
-        <v>✓ 23 junk removed</v>
+        <v>223 (merged dupes)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Duplicate slots</v>
+        <v>Lead↔Contact duplicates</v>
       </c>
       <c r="B5" t="str">
-        <v>9</v>
+        <v>241</v>
       </c>
       <c r="C5" t="str">
         <v>0</v>
       </c>
-      <c r="D5" t="str">
-        <v>✓ deduped</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Records with Layout</v>
+        <v>Account name duplicates</v>
       </c>
       <c r="B6" t="str">
-        <v>0/259</v>
+        <v>37 groups</v>
       </c>
       <c r="C6" t="str">
-        <v>259/259</v>
-      </c>
-      <c r="D6" t="str">
-        <v>✓ 100%</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Source_Form coverage</v>
+        <v>Junk fields in Leads module</v>
       </c>
       <c r="B7" t="str">
-        <v>56%</v>
+        <v>14 (23 IDs)</v>
       </c>
       <c r="C7" t="str">
-        <v>100%</v>
-      </c>
-      <c r="D7" t="str">
-        <v>+44pp</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Company coverage</v>
+        <v>Layout slots</v>
       </c>
       <c r="B8" t="str">
-        <v>61%</v>
+        <v>83</v>
       </c>
       <c r="C8" t="str">
-        <v>100%</v>
-      </c>
-      <c r="D8" t="str">
-        <v>+39pp</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Amyloidosis_Type</v>
+        <v>Source_Form coverage</v>
       </c>
       <c r="B9" t="str">
-        <v>7%</v>
+        <v>56%</v>
       </c>
       <c r="C9" t="str">
-        <v>14%</v>
-      </c>
-      <c r="D9" t="str">
-        <v>+7pp (limited source data)</v>
+        <v>88%</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Form_Submission_Date</v>
+        <v>Company / Institution_Name</v>
       </c>
       <c r="B10" t="str">
-        <v>0%</v>
+        <v>61% / 97%</v>
       </c>
       <c r="C10" t="str">
-        <v>60%</v>
-      </c>
-      <c r="D10" t="str">
-        <v>+60pp</v>
+        <v>85% (now on Contacts)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Email coverage</v>
+        <v>Form_Submission_Date</v>
       </c>
       <c r="B11" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="C11" t="str">
-        <v>100%</v>
-      </c>
-      <c r="D11" t="str">
-        <v>=</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Institution_Name</v>
-      </c>
-      <c r="B12" t="str">
-        <v>97%</v>
-      </c>
-      <c r="C12" t="str">
-        <v>97%</v>
-      </c>
-      <c r="D12" t="str">
-        <v>=</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Professional_Designation</v>
-      </c>
-      <c r="B13" t="str">
-        <v>96%</v>
-      </c>
-      <c r="C13" t="str">
-        <v>96%</v>
-      </c>
-      <c r="D13" t="str">
-        <v>=</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Record_Type</v>
-      </c>
-      <c r="B14" t="str">
-        <v>99%</v>
-      </c>
-      <c r="C14" t="str">
-        <v>99%</v>
-      </c>
-      <c r="D14" t="str">
-        <v>=</v>
+        <v>57%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>